--- a/business_forms/044_transmission_specialist_referral_form--business_forms.xlsx
+++ b/business_forms/044_transmission_specialist_referral_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>kia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
+          <t>Kia</t>
         </is>
       </c>
     </row>
@@ -985,29 +985,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kia</t>
+          <t>mazda</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kia</t>
+          <t>Mazda</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vehicle_make_choices</t>
+          <t>transmission_problem_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mazda</t>
+          <t>low_transmission_fluid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mazda</t>
+          <t>Low transmission fluid</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>low_transmission_fluid</t>
+          <t>gear_slipping</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Low transmission fluid</t>
+          <t>Gear slipping</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gear_slipping</t>
+          <t>leaking_transmission_fluid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gear slipping</t>
+          <t>Leaking transmission fluid</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>leaking_transmission_fluid</t>
+          <t>grinding_or_grinding_noises</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Leaking transmission fluid</t>
+          <t>Grinding or grinding noises</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>grinding_or_grinding_noises</t>
+          <t>slipping_or_slipping_between_gears</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Grinding or grinding noises</t>
+          <t>Slipping or slipping between gears</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>slipping_or_slipping_between_gears</t>
+          <t>vibration_while_driving</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slipping or slipping between gears</t>
+          <t>Vibration while driving</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vibration_while_driving</t>
+          <t>vibration_while_shifting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vibration while driving</t>
+          <t>Vibration while shifting</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vibration_while_shifting</t>
+          <t>noisy_gears</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vibration while shifting</t>
+          <t>Noisy gears</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>noisy_gears</t>
+          <t>loss_of_power</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Noisy gears</t>
+          <t>Loss of power</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>loss_of_power</t>
+          <t>slipping</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Loss of power</t>
+          <t>Slipping</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>slipping</t>
+          <t>noisy_transmission</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Slipping</t>
+          <t>Noisy transmission</t>
         </is>
       </c>
     </row>
@@ -1189,29 +1189,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>noisy_transmission</t>
+          <t>no_transmission_engagement</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Noisy transmission</t>
+          <t>No transmission engagement</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>transmission_problem_choices</t>
+          <t>service_request_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no_transmission_engagement</t>
+          <t>automatic_transmission_repair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No transmission engagement</t>
+          <t>Automatic Transmission Repair</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>automatic_transmission_repair</t>
+          <t>manual_transmission_repair</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Automatic Transmission Repair</t>
+          <t>Manual Transmission Repair</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>manual_transmission_repair</t>
+          <t>transmission_replacement</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Manual Transmission Repair</t>
+          <t>Transmission Replacement</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>transmission_replacement</t>
+          <t>transmission_maintenance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Transmission Replacement</t>
+          <t>Transmission Maintenance</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>transmission_maintenance</t>
+          <t>transmission_fluid_replacement</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Transmission Maintenance</t>
+          <t>Transmission Fluid Replacement</t>
         </is>
       </c>
     </row>
@@ -1291,29 +1291,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>transmission_fluid_replacement</t>
+          <t>other_(specify)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Transmission Fluid Replacement</t>
+          <t>Other (Specify)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>service_request_choices</t>
+          <t>transmission_specialist_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>other_(specify)</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1325,27 +1325,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>transmission_specialist_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
